--- a/data/service_catalog.xlsx
+++ b/data/service_catalog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/302172_cognizant_com/Documents/Desktop/RAG_ServiceCatalog/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/302172_cognizant_com/Documents/Desktop/RAG_ServiceCatalog/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="10" documentId="8_{619CAD23-3F6A-493C-8DD2-9A2765EC0A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4392238-25F7-4891-B903-3D0A19FE6889}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F0C6C304-FB4F-4418-91B9-1B67A827308A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F0C6C304-FB4F-4418-91B9-1B67A827308A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/service_catalog.xlsx
+++ b/data/service_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/302172_cognizant_com/Documents/Desktop/RAG_ServiceCatalog/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{619CAD23-3F6A-493C-8DD2-9A2765EC0A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4392238-25F7-4891-B903-3D0A19FE6889}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{619CAD23-3F6A-493C-8DD2-9A2765EC0A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A927FFB7-19C1-4B84-B12B-44F1686DBBFF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F0C6C304-FB4F-4418-91B9-1B67A827308A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="41">
   <si>
     <t>WU Id</t>
   </si>
@@ -59,9 +59,6 @@
     <t>Project related Services</t>
   </si>
   <si>
-    <t>Column1</t>
-  </si>
-  <si>
     <t>PMS_WU_2212</t>
   </si>
   <si>
@@ -80,18 +77,12 @@
     <t>Provisioning</t>
   </si>
   <si>
-    <t>"L3 Co-ordination Activity - Measured per Stream   of effort:</t>
-  </si>
-  <si>
     <t>IMS_WU_7036</t>
   </si>
   <si>
     <t>Configuration</t>
   </si>
   <si>
-    <t>L3 Implementation activity - Measured per job</t>
-  </si>
-  <si>
     <t>IMS_WU_7037</t>
   </si>
   <si>
@@ -132,6 +123,42 @@
   </si>
   <si>
     <t>Job decommission or Deleted an existing Job. Required additional approvals.</t>
+  </si>
+  <si>
+    <t>PMS_WU_0183</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>Firewall/Switching/Routing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TID Implementation (LAN/WAN/Wifi) </t>
+  </si>
+  <si>
+    <t>PMS_WU_0186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation of new switch stack </t>
+  </si>
+  <si>
+    <t>PMS_WU_0187</t>
+  </si>
+  <si>
+    <t>Replacing switch stack</t>
+  </si>
+  <si>
+    <t>PMS_WU_0192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Develop and publish required DR processes and procedures (Per service/platform) </t>
+  </si>
+  <si>
+    <t>PMS_WU_8060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New Vlan Creation  </t>
   </si>
 </sst>
 </file>
@@ -229,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -237,9 +264,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -260,6 +284,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -595,8 +628,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DC323F6-7D58-4C18-9DC0-263FFDA0A5F0}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="21.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
@@ -604,10 +637,9 @@
     <col min="4" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="73.140625" customWidth="1"/>
-    <col min="8" max="8" width="47.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -629,164 +661,258 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="B3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="7" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="G8" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="G9" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="E10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="G11" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="F12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>14</v>
+      <c r="G12" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
